--- a/admin/templates/purchase_receipt_template.xlsx
+++ b/admin/templates/purchase_receipt_template.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\Nas3fee7b\資料\愛心送餐\菜單成本相關\採購驗收單\115年度\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\psi_frontend_v268_purchase_download_no_popup_20260409\admin\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DD61C6D-5554-4A3D-B4D3-E7FB38A45F3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7790C2D-112E-4E61-BF04-A592860FECE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="617" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -435,42 +435,9 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="11" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="11" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="12" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="12" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="11" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -480,51 +447,15 @@
     <xf numFmtId="180" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="8" fontId="6" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="6" fontId="6" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="11" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="15" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="15" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="16" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="14" fillId="2" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="3" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -548,6 +479,75 @@
     </xf>
     <xf numFmtId="177" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="15" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="15" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="8" fontId="6" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="6" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="2" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="11" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="12" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="12" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="11" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -862,7 +862,7 @@
   <dimension ref="A1:P22"/>
   <sheetFormatPr defaultRowHeight="28.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.6640625" style="24" customWidth="1"/>
+    <col min="1" max="1" width="4.6640625" style="13" customWidth="1"/>
     <col min="2" max="2" width="24.44140625" style="1" customWidth="1"/>
     <col min="3" max="3" width="26.88671875" style="1" customWidth="1"/>
     <col min="4" max="4" width="16.21875" style="1" customWidth="1"/>
@@ -1448,56 +1448,56 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
-      <c r="E1" s="44"/>
-      <c r="F1" s="44"/>
-      <c r="G1" s="44"/>
-      <c r="H1" s="44"/>
-      <c r="I1" s="44"/>
-      <c r="J1" s="44"/>
-      <c r="K1" s="44"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
+      <c r="I1" s="21"/>
+      <c r="J1" s="21"/>
+      <c r="K1" s="21"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-      <c r="F2" s="24"/>
-      <c r="G2" s="24"/>
-      <c r="H2" s="24"/>
-      <c r="I2" s="24"/>
-      <c r="J2" s="45" t="s">
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="13"/>
+      <c r="J2" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="K2" s="45"/>
-      <c r="L2" s="46" t="s">
+      <c r="K2" s="22"/>
+      <c r="L2" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="M2" s="46"/>
+      <c r="M2" s="23"/>
     </row>
     <row r="3" spans="1:16" ht="28.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="47">
+      <c r="A3" s="24">
         <v>46111</v>
       </c>
-      <c r="B3" s="47"/>
-      <c r="C3" s="47"/>
-      <c r="D3" s="47"/>
-      <c r="E3" s="47"/>
-      <c r="F3" s="47"/>
-      <c r="G3" s="47"/>
-      <c r="H3" s="47"/>
-      <c r="I3" s="48">
+      <c r="B3" s="24"/>
+      <c r="C3" s="24"/>
+      <c r="D3" s="24"/>
+      <c r="E3" s="24"/>
+      <c r="F3" s="24"/>
+      <c r="G3" s="24"/>
+      <c r="H3" s="24"/>
+      <c r="I3" s="25">
         <v>46112</v>
       </c>
-      <c r="J3" s="48"/>
-      <c r="K3" s="48"/>
-      <c r="L3" s="48"/>
-      <c r="M3" s="48"/>
+      <c r="J3" s="25"/>
+      <c r="K3" s="25"/>
+      <c r="L3" s="25"/>
+      <c r="M3" s="25"/>
     </row>
     <row r="4" spans="1:16" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -1543,22 +1543,22 @@
       <c r="A5" s="9">
         <v>1</v>
       </c>
-      <c r="B5" s="35"/>
-      <c r="C5" s="36"/>
-      <c r="D5" s="35"/>
-      <c r="E5" s="37"/>
-      <c r="F5" s="38"/>
-      <c r="G5" s="14"/>
-      <c r="H5" s="26"/>
-      <c r="I5" s="29"/>
-      <c r="J5" s="16"/>
-      <c r="K5" s="27" t="s">
-        <v>11</v>
-      </c>
-      <c r="L5" s="27" t="s">
-        <v>11</v>
-      </c>
-      <c r="M5" s="17"/>
+      <c r="B5" s="26"/>
+      <c r="C5" s="27"/>
+      <c r="D5" s="26"/>
+      <c r="E5" s="28"/>
+      <c r="F5" s="29"/>
+      <c r="G5" s="30"/>
+      <c r="H5" s="31"/>
+      <c r="I5" s="32"/>
+      <c r="J5" s="33"/>
+      <c r="K5" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="L5" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="M5" s="11"/>
       <c r="P5" s="1"/>
     </row>
     <row r="6" spans="1:16" ht="39.6" x14ac:dyDescent="0.3">
@@ -1566,65 +1566,65 @@
         <v>2</v>
       </c>
       <c r="B6" s="34"/>
-      <c r="C6" s="14"/>
-      <c r="D6" s="35"/>
-      <c r="E6" s="37"/>
-      <c r="F6" s="38"/>
-      <c r="G6" s="14"/>
-      <c r="H6" s="11"/>
-      <c r="I6" s="15"/>
-      <c r="J6" s="16"/>
-      <c r="K6" s="27" t="s">
-        <v>11</v>
-      </c>
-      <c r="L6" s="27" t="s">
-        <v>11</v>
-      </c>
-      <c r="M6" s="17"/>
+      <c r="C6" s="30"/>
+      <c r="D6" s="26"/>
+      <c r="E6" s="28"/>
+      <c r="F6" s="29"/>
+      <c r="G6" s="30"/>
+      <c r="H6" s="35"/>
+      <c r="I6" s="36"/>
+      <c r="J6" s="33"/>
+      <c r="K6" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="L6" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="M6" s="11"/>
       <c r="P6" s="1"/>
     </row>
     <row r="7" spans="1:16" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A7" s="9">
         <v>3</v>
       </c>
-      <c r="B7" s="35"/>
-      <c r="C7" s="36"/>
-      <c r="D7" s="35"/>
-      <c r="E7" s="37"/>
-      <c r="F7" s="38"/>
-      <c r="G7" s="14"/>
-      <c r="H7" s="11"/>
-      <c r="I7" s="15"/>
-      <c r="J7" s="16"/>
-      <c r="K7" s="27" t="s">
-        <v>11</v>
-      </c>
-      <c r="L7" s="27" t="s">
-        <v>11</v>
-      </c>
-      <c r="M7" s="17"/>
+      <c r="B7" s="26"/>
+      <c r="C7" s="27"/>
+      <c r="D7" s="26"/>
+      <c r="E7" s="28"/>
+      <c r="F7" s="29"/>
+      <c r="G7" s="30"/>
+      <c r="H7" s="35"/>
+      <c r="I7" s="36"/>
+      <c r="J7" s="33"/>
+      <c r="K7" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="L7" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="M7" s="11"/>
       <c r="P7" s="1"/>
     </row>
     <row r="8" spans="1:16" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A8" s="9">
         <v>4</v>
       </c>
-      <c r="B8" s="35"/>
-      <c r="C8" s="40"/>
-      <c r="D8" s="35"/>
-      <c r="E8" s="37"/>
-      <c r="F8" s="38"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="15"/>
-      <c r="J8" s="16"/>
-      <c r="K8" s="27" t="s">
-        <v>11</v>
-      </c>
-      <c r="L8" s="27" t="s">
-        <v>11</v>
-      </c>
-      <c r="M8" s="17"/>
+      <c r="B8" s="26"/>
+      <c r="C8" s="37"/>
+      <c r="D8" s="26"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="29"/>
+      <c r="G8" s="30"/>
+      <c r="H8" s="35"/>
+      <c r="I8" s="36"/>
+      <c r="J8" s="33"/>
+      <c r="K8" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="L8" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="M8" s="11"/>
       <c r="P8" s="1"/>
     </row>
     <row r="9" spans="1:16" ht="39.6" x14ac:dyDescent="0.3">
@@ -1633,151 +1633,151 @@
       </c>
       <c r="B9" s="34"/>
       <c r="C9" s="34"/>
-      <c r="D9" s="35"/>
-      <c r="E9" s="37"/>
-      <c r="F9" s="38"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="31"/>
-      <c r="I9" s="15"/>
-      <c r="J9" s="16"/>
-      <c r="K9" s="27" t="s">
-        <v>11</v>
-      </c>
-      <c r="L9" s="27" t="s">
-        <v>11</v>
-      </c>
-      <c r="M9" s="39"/>
+      <c r="D9" s="26"/>
+      <c r="E9" s="28"/>
+      <c r="F9" s="29"/>
+      <c r="G9" s="30"/>
+      <c r="H9" s="38"/>
+      <c r="I9" s="36"/>
+      <c r="J9" s="33"/>
+      <c r="K9" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="L9" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="M9" s="17"/>
       <c r="P9" s="1"/>
     </row>
     <row r="10" spans="1:16" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A10" s="9">
         <v>6</v>
       </c>
-      <c r="B10" s="35"/>
+      <c r="B10" s="26"/>
       <c r="C10" s="34"/>
-      <c r="D10" s="35"/>
-      <c r="E10" s="37"/>
-      <c r="F10" s="38"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="11"/>
-      <c r="I10" s="15"/>
-      <c r="J10" s="11"/>
-      <c r="K10" s="27" t="s">
-        <v>11</v>
-      </c>
-      <c r="L10" s="27" t="s">
-        <v>11</v>
-      </c>
-      <c r="M10" s="39"/>
+      <c r="D10" s="26"/>
+      <c r="E10" s="28"/>
+      <c r="F10" s="29"/>
+      <c r="G10" s="30"/>
+      <c r="H10" s="35"/>
+      <c r="I10" s="36"/>
+      <c r="J10" s="35"/>
+      <c r="K10" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="L10" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="M10" s="17"/>
       <c r="P10" s="1"/>
     </row>
     <row r="11" spans="1:16" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A11" s="9">
         <v>7</v>
       </c>
-      <c r="B11" s="35"/>
+      <c r="B11" s="26"/>
       <c r="C11" s="34"/>
-      <c r="D11" s="35"/>
-      <c r="E11" s="37"/>
-      <c r="F11" s="38"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="15"/>
-      <c r="J11" s="11"/>
-      <c r="K11" s="27" t="s">
-        <v>11</v>
-      </c>
-      <c r="L11" s="27" t="s">
-        <v>11</v>
-      </c>
-      <c r="M11" s="39"/>
+      <c r="D11" s="26"/>
+      <c r="E11" s="28"/>
+      <c r="F11" s="29"/>
+      <c r="G11" s="30"/>
+      <c r="H11" s="35"/>
+      <c r="I11" s="36"/>
+      <c r="J11" s="35"/>
+      <c r="K11" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="L11" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="M11" s="17"/>
       <c r="P11" s="1"/>
     </row>
     <row r="12" spans="1:16" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A12" s="9">
         <v>8</v>
       </c>
-      <c r="B12" s="35"/>
+      <c r="B12" s="26"/>
       <c r="C12" s="34"/>
-      <c r="D12" s="35"/>
-      <c r="E12" s="37"/>
-      <c r="F12" s="38"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="15"/>
-      <c r="J12" s="16"/>
-      <c r="K12" s="27" t="s">
-        <v>11</v>
-      </c>
-      <c r="L12" s="27" t="s">
-        <v>11</v>
-      </c>
-      <c r="M12" s="39"/>
+      <c r="D12" s="26"/>
+      <c r="E12" s="28"/>
+      <c r="F12" s="29"/>
+      <c r="G12" s="30"/>
+      <c r="H12" s="35"/>
+      <c r="I12" s="36"/>
+      <c r="J12" s="33"/>
+      <c r="K12" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="L12" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="M12" s="17"/>
       <c r="P12" s="1"/>
     </row>
     <row r="13" spans="1:16" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A13" s="9">
         <v>9</v>
       </c>
-      <c r="B13" s="35"/>
+      <c r="B13" s="26"/>
       <c r="C13" s="34"/>
-      <c r="D13" s="35"/>
-      <c r="E13" s="37"/>
-      <c r="F13" s="38"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="11"/>
-      <c r="I13" s="15"/>
-      <c r="J13" s="16"/>
-      <c r="K13" s="27" t="s">
-        <v>11</v>
-      </c>
-      <c r="L13" s="27" t="s">
-        <v>11</v>
-      </c>
-      <c r="M13" s="39"/>
+      <c r="D13" s="26"/>
+      <c r="E13" s="28"/>
+      <c r="F13" s="29"/>
+      <c r="G13" s="30"/>
+      <c r="H13" s="35"/>
+      <c r="I13" s="36"/>
+      <c r="J13" s="33"/>
+      <c r="K13" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="L13" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="M13" s="17"/>
     </row>
     <row r="14" spans="1:16" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A14" s="9">
         <v>10</v>
       </c>
-      <c r="B14" s="35"/>
-      <c r="C14" s="36"/>
-      <c r="D14" s="35"/>
-      <c r="E14" s="37"/>
-      <c r="F14" s="13"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="11"/>
-      <c r="I14" s="15"/>
-      <c r="J14" s="15"/>
-      <c r="K14" s="27" t="s">
-        <v>11</v>
-      </c>
-      <c r="L14" s="27" t="s">
-        <v>11</v>
-      </c>
-      <c r="M14" s="17"/>
+      <c r="B14" s="26"/>
+      <c r="C14" s="27"/>
+      <c r="D14" s="26"/>
+      <c r="E14" s="28"/>
+      <c r="F14" s="39"/>
+      <c r="G14" s="30"/>
+      <c r="H14" s="35"/>
+      <c r="I14" s="36"/>
+      <c r="J14" s="36"/>
+      <c r="K14" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="L14" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="M14" s="11"/>
       <c r="P14" s="1"/>
     </row>
     <row r="15" spans="1:16" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A15" s="9">
         <v>11</v>
       </c>
-      <c r="B15" s="35"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="35"/>
-      <c r="E15" s="37"/>
-      <c r="F15" s="13"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="11"/>
-      <c r="I15" s="15"/>
-      <c r="J15" s="16"/>
-      <c r="K15" s="27" t="s">
-        <v>11</v>
-      </c>
-      <c r="L15" s="27" t="s">
-        <v>11</v>
-      </c>
-      <c r="M15" s="17"/>
+      <c r="B15" s="26"/>
+      <c r="C15" s="30"/>
+      <c r="D15" s="26"/>
+      <c r="E15" s="28"/>
+      <c r="F15" s="39"/>
+      <c r="G15" s="30"/>
+      <c r="H15" s="35"/>
+      <c r="I15" s="36"/>
+      <c r="J15" s="33"/>
+      <c r="K15" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="L15" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="M15" s="11"/>
     </row>
     <row r="16" spans="1:16" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A16" s="9">
@@ -1785,42 +1785,42 @@
       </c>
       <c r="B16" s="34"/>
       <c r="C16" s="34"/>
-      <c r="D16" s="35"/>
-      <c r="E16" s="37"/>
-      <c r="F16" s="13"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="11"/>
-      <c r="I16" s="15"/>
-      <c r="J16" s="15"/>
-      <c r="K16" s="27" t="s">
-        <v>11</v>
-      </c>
-      <c r="L16" s="27" t="s">
-        <v>11</v>
-      </c>
-      <c r="M16" s="17"/>
+      <c r="D16" s="26"/>
+      <c r="E16" s="28"/>
+      <c r="F16" s="39"/>
+      <c r="G16" s="30"/>
+      <c r="H16" s="35"/>
+      <c r="I16" s="36"/>
+      <c r="J16" s="36"/>
+      <c r="K16" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="L16" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="M16" s="11"/>
       <c r="P16" s="1"/>
     </row>
     <row r="17" spans="1:16" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A17" s="9">
         <v>13</v>
       </c>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="35"/>
-      <c r="E17" s="37"/>
-      <c r="F17" s="13"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="11"/>
-      <c r="I17" s="15"/>
-      <c r="J17" s="15"/>
-      <c r="K17" s="27" t="s">
-        <v>11</v>
-      </c>
-      <c r="L17" s="27" t="s">
-        <v>11</v>
-      </c>
-      <c r="M17" s="17"/>
+      <c r="B17" s="30"/>
+      <c r="C17" s="30"/>
+      <c r="D17" s="26"/>
+      <c r="E17" s="28"/>
+      <c r="F17" s="39"/>
+      <c r="G17" s="30"/>
+      <c r="H17" s="35"/>
+      <c r="I17" s="36"/>
+      <c r="J17" s="36"/>
+      <c r="K17" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="L17" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="M17" s="11"/>
     </row>
     <row r="18" spans="1:16" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A18" s="9">
@@ -1828,88 +1828,88 @@
       </c>
       <c r="B18" s="34"/>
       <c r="C18" s="34"/>
-      <c r="D18" s="35"/>
-      <c r="E18" s="37"/>
-      <c r="F18" s="13"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="11"/>
-      <c r="I18" s="15"/>
-      <c r="J18" s="15"/>
-      <c r="K18" s="27" t="s">
-        <v>11</v>
-      </c>
-      <c r="L18" s="27" t="s">
-        <v>11</v>
-      </c>
-      <c r="M18" s="17"/>
+      <c r="D18" s="26"/>
+      <c r="E18" s="28"/>
+      <c r="F18" s="39"/>
+      <c r="G18" s="30"/>
+      <c r="H18" s="35"/>
+      <c r="I18" s="36"/>
+      <c r="J18" s="36"/>
+      <c r="K18" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="L18" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="M18" s="11"/>
       <c r="P18" s="1"/>
     </row>
     <row r="19" spans="1:16" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A19" s="9">
         <v>15</v>
       </c>
-      <c r="B19" s="30"/>
-      <c r="C19" s="30"/>
-      <c r="D19" s="12"/>
-      <c r="E19" s="18"/>
-      <c r="F19" s="13"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="11"/>
-      <c r="I19" s="15"/>
-      <c r="J19" s="16"/>
-      <c r="K19" s="27" t="s">
-        <v>11</v>
-      </c>
-      <c r="L19" s="27" t="s">
-        <v>11</v>
-      </c>
-      <c r="M19" s="17"/>
+      <c r="B19" s="40"/>
+      <c r="C19" s="40"/>
+      <c r="D19" s="41"/>
+      <c r="E19" s="42"/>
+      <c r="F19" s="39"/>
+      <c r="G19" s="30"/>
+      <c r="H19" s="35"/>
+      <c r="I19" s="36"/>
+      <c r="J19" s="33"/>
+      <c r="K19" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="L19" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="M19" s="11"/>
     </row>
     <row r="20" spans="1:16" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="9">
         <v>16</v>
       </c>
-      <c r="B20" s="21"/>
-      <c r="C20" s="21"/>
-      <c r="D20" s="32"/>
-      <c r="E20" s="19"/>
-      <c r="F20" s="33"/>
-      <c r="G20" s="20"/>
-      <c r="H20" s="21"/>
-      <c r="I20" s="22"/>
-      <c r="J20" s="22"/>
-      <c r="K20" s="28" t="s">
-        <v>11</v>
-      </c>
-      <c r="L20" s="28" t="s">
-        <v>11</v>
-      </c>
-      <c r="M20" s="23"/>
-    </row>
-    <row r="21" spans="1:16" s="42" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="43" t="s">
+      <c r="B20" s="43"/>
+      <c r="C20" s="43"/>
+      <c r="D20" s="44"/>
+      <c r="E20" s="45"/>
+      <c r="F20" s="46"/>
+      <c r="G20" s="47"/>
+      <c r="H20" s="43"/>
+      <c r="I20" s="48"/>
+      <c r="J20" s="48"/>
+      <c r="K20" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="L20" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="M20" s="12"/>
+    </row>
+    <row r="21" spans="1:16" s="19" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="B21" s="43"/>
-      <c r="C21" s="43"/>
-      <c r="D21" s="43"/>
-      <c r="E21" s="43"/>
-      <c r="F21" s="43"/>
-      <c r="G21" s="43"/>
-      <c r="H21" s="43"/>
-      <c r="I21" s="43"/>
-      <c r="J21" s="43"/>
-      <c r="K21" s="43"/>
-      <c r="L21" s="43"/>
-      <c r="M21" s="43"/>
-      <c r="N21" s="41"/>
+      <c r="B21" s="20"/>
+      <c r="C21" s="20"/>
+      <c r="D21" s="20"/>
+      <c r="E21" s="20"/>
+      <c r="F21" s="20"/>
+      <c r="G21" s="20"/>
+      <c r="H21" s="20"/>
+      <c r="I21" s="20"/>
+      <c r="J21" s="20"/>
+      <c r="K21" s="20"/>
+      <c r="L21" s="20"/>
+      <c r="M21" s="20"/>
+      <c r="N21" s="18"/>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.3">
       <c r="G22" s="10"/>
-      <c r="I22" s="25"/>
-      <c r="J22" s="25"/>
-      <c r="K22" s="25"/>
-      <c r="L22" s="25"/>
+      <c r="I22" s="14"/>
+      <c r="J22" s="14"/>
+      <c r="K22" s="14"/>
+      <c r="L22" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="6">

--- a/admin/templates/purchase_receipt_template.xlsx
+++ b/admin/templates/purchase_receipt_template.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\psi_frontend_v268_purchase_download_no_popup_20260409\admin\templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\psi_frontend_v269_download_notice_and_shop_filter_buttons_20260409\admin\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7790C2D-112E-4E61-BF04-A592860FECE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C80F8B15-2A3B-4E6A-BF07-C50871DDA8F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="617" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
